--- a/25_DS_Weekend_Club/Attendance.xlsx
+++ b/25_DS_Weekend_Club/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\25_DS_Weekend_Club\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871AEB4D-EC07-4745-8D61-0B2B43E7D349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6BD3C2-BB8D-4187-8EAF-421A41483901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EC4D2ACC-CD4C-486C-BF30-05E3BE69212B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="10">
   <si>
     <t>Vedant</t>
   </si>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A55502-5BFD-4527-B88F-192204BA3B39}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -485,6 +485,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>45724</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45725</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/25_DS_Weekend_Club/Attendance.xlsx
+++ b/25_DS_Weekend_Club/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\25_DS_Weekend_Club\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6BD3C2-BB8D-4187-8EAF-421A41483901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208B589C-FCDC-471E-8C0E-D06D0D4ABC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EC4D2ACC-CD4C-486C-BF30-05E3BE69212B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="10">
   <si>
     <t>Vedant</t>
   </si>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A55502-5BFD-4527-B88F-192204BA3B39}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -537,6 +537,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45732</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/25_DS_Weekend_Club/Attendance.xlsx
+++ b/25_DS_Weekend_Club/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\25_DS_Weekend_Club\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208B589C-FCDC-471E-8C0E-D06D0D4ABC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CA44CD-F5B8-4A78-B94C-17367E36A762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EC4D2ACC-CD4C-486C-BF30-05E3BE69212B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="10">
   <si>
     <t>Vedant</t>
   </si>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A55502-5BFD-4527-B88F-192204BA3B39}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -563,6 +563,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45739</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45745</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/25_DS_Weekend_Club/Attendance.xlsx
+++ b/25_DS_Weekend_Club/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\25_DS_Weekend_Club\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CA44CD-F5B8-4A78-B94C-17367E36A762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E90D8B9-2C0F-4715-AFBA-73FC463C2497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EC4D2ACC-CD4C-486C-BF30-05E3BE69212B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="10">
   <si>
     <t>Vedant</t>
   </si>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A55502-5BFD-4527-B88F-192204BA3B39}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -615,6 +615,84 @@
         <v>9</v>
       </c>
     </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45746</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45752</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45753</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/25_DS_Weekend_Club/Attendance.xlsx
+++ b/25_DS_Weekend_Club/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\25_DS_Weekend_Club\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E90D8B9-2C0F-4715-AFBA-73FC463C2497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE0D6A2-8559-4D83-91CA-651CABED1F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EC4D2ACC-CD4C-486C-BF30-05E3BE69212B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="10">
   <si>
     <t>Vedant</t>
   </si>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A55502-5BFD-4527-B88F-192204BA3B39}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -693,6 +693,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45759</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45760</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
